--- a/docs/rag_execution_evaluation_results/new/dementia-mxbai-embed-large-1200-100-4/ragas/dementia_metrics.xlsx
+++ b/docs/rag_execution_evaluation_results/new/dementia-mxbai-embed-large-1200-100-4/ragas/dementia_metrics.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5999997897223569</v>
+        <v>0.9415836158000002</v>
       </c>
     </row>
     <row r="3">
